--- a/src/test/resources/test.xlsx
+++ b/src/test/resources/test.xlsx
@@ -18,6 +18,14 @@
     <sheet name="Picture" r:id="rId12" sheetId="10"/>
     <sheet name="Data Verification" r:id="rId13" sheetId="11"/>
   </sheets>
+  <definedNames>
+    <definedName name="TaxRate" comment="Default tax rate used across sheets.">0.17</definedName>
+    <definedName name="LocalRange" localSheetId="1">Formula!$A$1:$B$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="true">Table!$A$1:$C$4</definedName>
+  </definedNames>
+  <pivotCaches>
+    <pivotCache cacheId="2" r:id="rId14"/>
+  </pivotCaches>
 </workbook>
 </file>
 
@@ -52,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="266">
   <si>
     <t>Background</t>
   </si>
@@ -858,6 +866,60 @@
   </si>
   <si>
     <t>311414199301118910</t>
+  </si>
+  <si>
+    <t>Univer Docs</t>
+  </si>
+  <si>
+    <t>Go to Formula</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>Banana</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>first</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>second</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>third</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>East</t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>North</t>
   </si>
 </sst>
 </file>
@@ -16562,6 +16624,22 @@
     <xf numFmtId="0" fontId="1758" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true"/>
   </cellXfs>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:chart>
+    <c:plotArea>
+      <c:layout/>
+    </c:plotArea>
+    <c:plotVisOnly val="true"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16722,24 +16800,184 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Shape 1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2000250" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchor="t" rtlCol="false"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t>Hello shape!</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="1" name="Shape 1"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="0" name="Diagramm0"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="5334000" cy="3305175"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" createdVersion="3" minRefreshableVersion="3" refreshedVersion="3" refreshedBy="Apache POI" refreshedDate="1.778429986555E12" refreshOnLoad="true" r:id="rId1">
+  <cacheSource type="worksheet">
+    <worksheetSource sheet="PivotTableData" ref="A1:B4"/>
+  </cacheSource>
+  <cacheFields count="2">
+    <cacheField numFmtId="0" name="Region">
+      <sharedItems/>
+    </cacheField>
+    <cacheField numFmtId="0" name="Amount">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" multipleFieldFilters="false" indent="0" createdVersion="3" minRefreshableVersion="3" updatedVersion="3" itemPrintTitles="true" useAutoFormatting="true" applyNumberFormats="false" applyWidthHeightFormats="true" applyAlignmentFormats="false" applyPatternFormats="false" applyFontFormats="false" applyBorderFormats="false" cacheId="2" name="PivotTable2" dataCaption="Values">
+  <location firstDataCol="1" firstDataRow="1" firstHeaderRow="1" ref="A1:B2"/>
+  <pivotFields count="2">
+    <pivotField dataField="false" showAll="false"/>
+    <pivotField dataField="false" showAll="false"/>
+  </pivotFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showLastColumn="true" showColStripes="false" showRowStripes="false" showColHeaders="true" showRowHeaders="true"/>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" ref="E1:G4" displayName="DemoTable" name="DemoTable">
+  <tableColumns count="3">
+    <tableColumn id="1" name="Key"/>
+    <tableColumn id="2" name="Value"/>
+    <tableColumn id="3" name="Note"/>
+  </tableColumns>
+</table>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M34"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="true" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="true"/>
-    <col min="3" max="3" width="21.8515625" customWidth="true"/>
-    <col min="4" max="4" width="18.28125" customWidth="true"/>
-    <col min="5" max="5" width="19.42578125" customWidth="true"/>
-    <col min="6" max="6" width="17.42578125" customWidth="true"/>
-    <col min="7" max="7" width="19.7109375" customWidth="true"/>
-    <col min="8" max="8" width="18.7109375" customWidth="true"/>
-    <col min="9" max="9" width="18.28125" customWidth="true"/>
-    <col min="10" max="10" width="19.99609375" customWidth="true"/>
-    <col min="11" max="11" width="20.56640625" customWidth="true"/>
+    <col min="1" max="1" customWidth="true" width="18.7109375"/>
+    <col min="3" max="3" customWidth="true" width="21.8515625"/>
+    <col min="4" max="4" customWidth="true" width="18.28125"/>
+    <col min="5" max="5" customWidth="true" width="19.42578125"/>
+    <col min="6" max="6" customWidth="true" width="17.42578125"/>
+    <col min="7" max="7" customWidth="true" width="19.7109375"/>
+    <col min="8" max="8" customWidth="true" width="18.7109375"/>
+    <col min="9" max="9" customWidth="true" width="18.28125"/>
+    <col min="10" max="10" customWidth="true" width="19.99609375"/>
+    <col min="11" max="11" customWidth="true" width="20.56640625"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.0" customHeight="true">
@@ -16917,8 +17155,12 @@
     <row r="13" ht="15.0" customHeight="true">
       <c r="A13" s="133"/>
       <c r="B13" s="134"/>
-      <c r="C13" s="135"/>
-      <c r="D13" s="136"/>
+      <c r="C13" s="135" t="s">
+        <v>248</v>
+      </c>
+      <c r="D13" s="136" t="s">
+        <v>249</v>
+      </c>
       <c r="E13" s="137"/>
       <c r="F13" s="138"/>
       <c r="G13" s="139"/>
@@ -17253,6 +17495,10 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="K16:M19"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C13" r:id="rId1"/>
+    <hyperlink location="Formula!A1" ref="D13"/>
+  </hyperlinks>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
@@ -17262,7 +17508,7 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="true" baseColWidth="10"/>
   <cols>
-    <col min="9" max="9" width="14.99609375" customWidth="true"/>
+    <col min="9" max="9" customWidth="true" width="14.99609375"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17304,12 +17550,12 @@
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="true" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.56640625" customWidth="true"/>
-    <col min="3" max="3" width="20.421875" customWidth="true"/>
-    <col min="4" max="4" width="28.56640625" customWidth="true"/>
-    <col min="5" max="5" width="25.70703125" customWidth="true"/>
-    <col min="7" max="7" width="25.421875" customWidth="true"/>
-    <col min="8" max="8" width="17.8515625" customWidth="true"/>
+    <col min="1" max="1" customWidth="true" width="15.56640625"/>
+    <col min="3" max="3" customWidth="true" width="20.421875"/>
+    <col min="4" max="4" customWidth="true" width="28.56640625"/>
+    <col min="5" max="5" customWidth="true" width="25.70703125"/>
+    <col min="7" max="7" customWidth="true" width="25.421875"/>
+    <col min="8" max="8" customWidth="true" width="17.8515625"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17498,6 +17744,15 @@
       <c r="I8" s="1754"/>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" sqref="A1:A10" allowBlank="true" errorStyle="stop" showErrorMessage="true" errorTitle="Invalid" error="Please choose Yes / No / Maybe">
+      <formula1>"Yes,No,Maybe"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" sqref="B1:B10" allowBlank="true" errorStyle="stop" showInputMessage="true" promptTitle="Range" prompt="Enter integer 1..100">
+      <formula1>1</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
@@ -17507,16 +17762,16 @@
   <dimension ref="A1:K39"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="true" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.8515625" customWidth="true"/>
-    <col min="3" max="3" width="14.99609375" customWidth="true"/>
-    <col min="4" max="4" width="11.7109375" customWidth="true"/>
-    <col min="5" max="5" width="10.140625" customWidth="true"/>
-    <col min="6" max="6" width="11.99609375" customWidth="true"/>
-    <col min="7" max="7" width="17.56640625" customWidth="true"/>
-    <col min="8" max="8" width="6.85546875" customWidth="true"/>
-    <col min="9" max="9" width="27.421875" customWidth="true"/>
-    <col min="10" max="10" width="8.0" customWidth="true"/>
-    <col min="11" max="11" width="8.0" customWidth="true"/>
+    <col min="1" max="1" customWidth="true" width="15.8515625"/>
+    <col min="3" max="3" customWidth="true" width="14.99609375"/>
+    <col min="4" max="4" customWidth="true" width="11.7109375"/>
+    <col min="5" max="5" customWidth="true" width="10.140625"/>
+    <col min="6" max="6" customWidth="true" width="11.99609375"/>
+    <col min="7" max="7" customWidth="true" width="17.56640625"/>
+    <col min="8" max="8" customWidth="true" width="6.85546875"/>
+    <col min="9" max="9" customWidth="true" width="27.421875"/>
+    <col min="10" max="10" customWidth="true" width="8.0"/>
+    <col min="11" max="11" customWidth="true" width="8.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18319,18 +18574,18 @@
   <dimension ref="A1:L30"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="true" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="true"/>
-    <col min="2" max="2" width="4.28515625" customWidth="true"/>
-    <col min="3" max="3" width="12.28125" customWidth="true"/>
-    <col min="4" max="4" width="12.140625" customWidth="true"/>
-    <col min="5" max="5" width="13.140625" customWidth="true"/>
-    <col min="6" max="6" width="13.28125" customWidth="true"/>
-    <col min="7" max="7" width="14.28125" customWidth="true"/>
-    <col min="8" max="8" width="14.28125" customWidth="true"/>
-    <col min="9" max="9" width="14.140625" customWidth="true"/>
-    <col min="10" max="10" width="12.85546875" customWidth="true"/>
-    <col min="11" max="11" width="13.7109375" customWidth="true"/>
-    <col min="12" max="12" width="13.7109375" customWidth="true"/>
+    <col min="1" max="1" customWidth="true" width="4.28515625"/>
+    <col min="2" max="2" customWidth="true" width="4.28515625"/>
+    <col min="3" max="3" customWidth="true" width="12.28125"/>
+    <col min="4" max="4" customWidth="true" width="12.140625"/>
+    <col min="5" max="5" customWidth="true" width="13.140625"/>
+    <col min="6" max="6" customWidth="true" width="13.28125"/>
+    <col min="7" max="7" customWidth="true" width="14.28125"/>
+    <col min="8" max="8" customWidth="true" width="14.28125"/>
+    <col min="9" max="9" customWidth="true" width="14.140625"/>
+    <col min="10" max="10" customWidth="true" width="12.85546875"/>
+    <col min="11" max="11" customWidth="true" width="13.7109375"/>
+    <col min="12" max="12" customWidth="true" width="13.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.0" customHeight="true">
@@ -19113,18 +19368,30 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="B1:M23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="true" baseColWidth="10"/>
   <sheetData>
     <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>24</v>
+      </c>
       <c r="B1" t="s" s="1119">
-        <v>96</v>
-      </c>
-      <c r="C1" s="1120"/>
+        <v>250</v>
+      </c>
+      <c r="C1" s="1120" t="s">
+        <v>251</v>
+      </c>
       <c r="D1" s="1121"/>
-      <c r="E1" s="1122"/>
-      <c r="F1" s="1123"/>
+      <c r="E1" s="1122" t="s">
+        <v>254</v>
+      </c>
+      <c r="F1" s="1123" t="s">
+        <v>255</v>
+      </c>
+      <c r="G1" t="s">
+        <v>137</v>
+      </c>
       <c r="I1" t="s" s="1124">
         <v>97</v>
       </c>
@@ -19134,20 +19401,66 @@
       <c r="M1" s="1128"/>
     </row>
     <row r="2">
-      <c r="B2" t="s" s="1129">
-        <v>98</v>
-      </c>
-      <c r="C2" t="s" s="1130">
-        <v>99</v>
+      <c r="A2" t="s" s="0">
+        <v>252</v>
+      </c>
+      <c r="B2" t="n" s="1129">
+        <v>10.0</v>
+      </c>
+      <c r="C2" t="n" s="1130">
+        <v>1.5</v>
       </c>
       <c r="D2" t="s" s="1131">
         <v>100</v>
       </c>
       <c r="E2" t="s" s="1132">
-        <v>101</v>
-      </c>
-      <c r="F2" t="s" s="1133">
-        <v>102</v>
+        <v>256</v>
+      </c>
+      <c r="F2" t="n" s="1133">
+        <v>1.0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="B3" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>0.8</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>3.2</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>261</v>
       </c>
     </row>
     <row r="9">
@@ -19317,6 +19630,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C4"/>
   <mergeCells count="6">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="I1:M1"/>
@@ -19326,6 +19640,9 @@
     <mergeCell ref="I17:M17"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -19334,15 +19651,15 @@
   <dimension ref="A1:N58"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="true" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" customWidth="true"/>
-    <col min="3" max="3" width="18.7109375" customWidth="true"/>
-    <col min="4" max="4" width="4.28515625" customWidth="true"/>
-    <col min="5" max="5" width="12.85546875" customWidth="true"/>
+    <col min="1" max="1" customWidth="true" width="14.42578125"/>
+    <col min="3" max="3" customWidth="true" width="18.7109375"/>
+    <col min="4" max="4" customWidth="true" width="4.28515625"/>
+    <col min="5" max="5" customWidth="true" width="12.85546875"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="true">
-      <c r="A1" t="s" s="1194">
-        <v>121</v>
+      <c r="A1" t="n" s="1194">
+        <v>1.0</v>
       </c>
       <c r="B1" s="1195"/>
       <c r="C1" s="1196"/>
@@ -19358,8 +19675,8 @@
       <c r="N1" s="1204"/>
     </row>
     <row r="2" ht="15.0" customHeight="true">
-      <c r="A2" t="s" s="1205">
-        <v>123</v>
+      <c r="A2" t="n" s="1205">
+        <v>3.0</v>
       </c>
       <c r="B2" t="s" s="1206">
         <v>124</v>
@@ -19386,7 +19703,7 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" t="n" s="1216">
-        <v>41671.0</v>
+        <v>2.0</v>
       </c>
       <c r="B3" t="n" s="1217">
         <v>30.0</v>
@@ -19411,7 +19728,7 @@
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" t="n" s="1227">
-        <v>41699.0</v>
+        <v>5.0</v>
       </c>
       <c r="B4" t="n" s="1228">
         <v>-60.0</v>
@@ -19436,7 +19753,7 @@
     </row>
     <row r="5" ht="15.0" customHeight="true">
       <c r="A5" t="n" s="1238">
-        <v>41730.0</v>
+        <v>4.0</v>
       </c>
       <c r="B5" t="n" s="1239">
         <v>80.0</v>
@@ -20214,6 +20531,22 @@
     <mergeCell ref="C28:E28"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <extLst>
+    <extLst>
+      <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
+        <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:sparklineGroup type="line">
+            <x14:sparklines>
+              <x14:sparkline>
+                <xm:f>Sparkline!A1:A5</xm:f>
+                <xm:sqref>B1</xm:sqref>
+              </x14:sparkline>
+            </x14:sparklines>
+          </x14:sparklineGroup>
+        </x14:sparklineGroups>
+      </ext>
+    </extLst>
+  </extLst>
 </worksheet>
 </file>
 
@@ -20222,7 +20555,7 @@
   <dimension ref="C3:C8"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="true" baseColWidth="10"/>
   <cols>
-    <col min="3" max="3" width="14.56640625" customWidth="true"/>
+    <col min="3" max="3" customWidth="true" width="14.56640625"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -20249,10 +20582,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1532">
-        <v>174</v>
+        <v>262</v>
       </c>
       <c r="B1" t="s" s="1533">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c r="C1" t="s" s="1534">
         <v>176</v>
@@ -20266,10 +20599,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="1537">
-        <v>179</v>
-      </c>
-      <c r="B2" t="s" s="1538">
-        <v>180</v>
+        <v>263</v>
+      </c>
+      <c r="B2" t="n" s="1538">
+        <v>10.0</v>
       </c>
       <c r="C2" t="s" s="1539">
         <v>181</v>
@@ -20283,10 +20616,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="1542">
-        <v>179</v>
-      </c>
-      <c r="B3" t="s" s="1543">
-        <v>180</v>
+        <v>264</v>
+      </c>
+      <c r="B3" t="n" s="1543">
+        <v>20.0</v>
       </c>
       <c r="C3" t="s" s="1544">
         <v>181</v>
@@ -20300,10 +20633,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="1547">
-        <v>179</v>
-      </c>
-      <c r="B4" t="s" s="1548">
-        <v>180</v>
+        <v>265</v>
+      </c>
+      <c r="B4" t="n" s="1548">
+        <v>15.0</v>
       </c>
       <c r="C4" t="s" s="1549">
         <v>181</v>
@@ -20584,14 +20917,16 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="true" baseColWidth="10"/>
   <sheetData>
     <row r="1" ht="15.0" customHeight="true">
-      <c r="A1" s="1627"/>
+      <c r="A1" s="1627" t="s">
+        <v>262</v>
+      </c>
       <c r="B1" t="s" s="1628">
-        <v>188</v>
+        <v>255</v>
       </c>
       <c r="C1" t="s" s="1629">
         <v>189</v>
@@ -20614,10 +20949,10 @@
     </row>
     <row r="2" ht="15.0" customHeight="true">
       <c r="A2" t="s" s="1635">
-        <v>195</v>
+        <v>263</v>
       </c>
       <c r="B2" t="n" s="1636">
-        <v>320.0</v>
+        <v>10.0</v>
       </c>
       <c r="C2" t="n" s="1637">
         <v>302.0</v>
@@ -20640,10 +20975,10 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" t="s" s="1643">
-        <v>196</v>
+        <v>264</v>
       </c>
       <c r="B3" t="n" s="1644">
-        <v>120.0</v>
+        <v>20.0</v>
       </c>
       <c r="C3" t="n" s="1645">
         <v>132.0</v>
@@ -20666,10 +21001,10 @@
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" t="s" s="1651">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="B4" t="n" s="1652">
-        <v>220.0</v>
+        <v>15.0</v>
       </c>
       <c r="C4" t="n" s="1653">
         <v>182.0</v>
@@ -20814,5 +21149,6 @@
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>